--- a/LCA Exports/Formate_InventoryAssessment.xlsx
+++ b/LCA Exports/Formate_InventoryAssessment.xlsx
@@ -814,7 +814,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Low Pressure Steam</t>
+          <t>Natural Gas (boiler)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -829,14 +829,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>kg_ng</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>448906.83359396</v>
+        <v>29681.87919602</v>
       </c>
       <c r="F8" t="n">
-        <v>139.0408764693</v>
+        <v>9.1934321107</v>
       </c>
     </row>
     <row r="9">
